--- a/static/media/templates/侵权词上传.xlsx
+++ b/static/media/templates/侵权词上传.xlsx
@@ -32,7 +32,7 @@
     <t>侵权词</t>
   </si>
   <si>
-    <t>侵权类型码（请输入数字）</t>
+    <t>侵权类型码(数字)</t>
   </si>
   <si>
     <t>这是一个侵权词，请把这行替换掉</t>

--- a/static/media/templates/侵权词上传.xlsx
+++ b/static/media/templates/侵权词上传.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="15060" windowHeight="13275"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>侵权词</t>
   </si>
   <si>
     <t>侵权类型码(数字)</t>
-  </si>
-  <si>
-    <t>这是一个侵权词，请把这行替换掉</t>
   </si>
   <si>
     <t>侵权类型码</t>
@@ -687,12 +684,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1219,119 +1213,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="46" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="10.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
         <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="E3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>4</v>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="E6" s="1">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="E7" s="1">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="E8" s="1">
-        <v>5</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="E9" s="1">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="E10" s="1">
-        <v>7</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>11</v>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="E11" s="1">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="E12" s="1">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="E13" s="1">
-        <v>10</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
